--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-08-31/2025-09-06</t>
+          <t>multi-venue - Sales Summary - 2025-09-07/2025-09-13</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18312.3</v>
+        <v>16015.76</v>
       </c>
       <c r="C3" t="n">
-        <v>18312.3</v>
+        <v>16015.76</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1248</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16110.77</v>
+        <v>8682.4</v>
       </c>
       <c r="C4" t="n">
-        <v>16110.77</v>
+        <v>8682.4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1016</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20974.27</v>
+        <v>18423.81</v>
       </c>
       <c r="C5" t="n">
-        <v>20974.27</v>
+        <v>18423.81</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1434</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15329.22</v>
+        <v>10847.3</v>
       </c>
       <c r="C6" t="n">
-        <v>15329.22</v>
+        <v>10847.3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>862</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4435.9</v>
+        <v>3843.74</v>
       </c>
       <c r="C7" t="n">
-        <v>4435.9</v>
+        <v>3843.74</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>371</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6876.4</v>
+        <v>4964.49</v>
       </c>
       <c r="C8" t="n">
-        <v>6876.4</v>
+        <v>4964.49</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>368</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82038.85999999999</v>
+        <v>62777.5</v>
       </c>
       <c r="C9" t="n">
-        <v>82038.85999999999</v>
+        <v>62777.5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-07/2025-09-13</t>
+          <t>multi-venue - Sales Summary - 2025-09-14/2025-09-20</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16015.76</v>
+        <v>17307.61</v>
       </c>
       <c r="C3" t="n">
-        <v>16015.76</v>
+        <v>17307.61</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1156</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8682.4</v>
+        <v>8692.73</v>
       </c>
       <c r="C4" t="n">
-        <v>8682.4</v>
+        <v>8692.73</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>602</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18423.81</v>
+        <v>19625.26</v>
       </c>
       <c r="C5" t="n">
-        <v>18423.81</v>
+        <v>19625.26</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1274</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10847.3</v>
+        <v>12815.44</v>
       </c>
       <c r="C6" t="n">
-        <v>10847.3</v>
+        <v>12815.44</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>718</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3843.74</v>
+        <v>6785.05</v>
       </c>
       <c r="C7" t="n">
-        <v>3843.74</v>
+        <v>6785.05</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>333</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4964.49</v>
+        <v>7480.1</v>
       </c>
       <c r="C8" t="n">
-        <v>4964.49</v>
+        <v>7480.1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>323</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62777.5</v>
+        <v>72706.19</v>
       </c>
       <c r="C9" t="n">
-        <v>62777.5</v>
+        <v>72706.19</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-14/2025-09-20</t>
+          <t>multi-venue - Sales Summary - 2025-09-21/2025-09-27</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17307.61</v>
+        <v>18772.2</v>
       </c>
       <c r="C3" t="n">
-        <v>17307.61</v>
+        <v>18772.2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1228</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8692.73</v>
+        <v>9708.709999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>8692.73</v>
+        <v>9708.709999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>580</v>
+        <v>626</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19625.26</v>
+        <v>19219.5</v>
       </c>
       <c r="C5" t="n">
-        <v>19625.26</v>
+        <v>19219.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1332</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12815.44</v>
+        <v>11469.65</v>
       </c>
       <c r="C6" t="n">
-        <v>12815.44</v>
+        <v>11469.65</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>785</v>
+        <v>745</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6785.05</v>
+        <v>4040.3</v>
       </c>
       <c r="C7" t="n">
-        <v>6785.05</v>
+        <v>4040.3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>585</v>
+        <v>372</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7480.1</v>
+        <v>6377.57</v>
       </c>
       <c r="C8" t="n">
-        <v>7480.1</v>
+        <v>6377.57</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>397</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72706.19</v>
+        <v>69587.93000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>72706.19</v>
+        <v>69587.93000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-21/2025-09-27</t>
+          <t>multi-venue - Sales Summary - 2025-09-28/2025-10-04</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18772.2</v>
+        <v>16144.73</v>
       </c>
       <c r="C3" t="n">
-        <v>18772.2</v>
+        <v>16144.73</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1348</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9708.709999999999</v>
+        <v>9341.639999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>9708.709999999999</v>
+        <v>9341.639999999999</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>626</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19219.5</v>
+        <v>18725.49</v>
       </c>
       <c r="C5" t="n">
-        <v>19219.5</v>
+        <v>18725.49</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1301</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11469.65</v>
+        <v>14083.68</v>
       </c>
       <c r="C6" t="n">
-        <v>11469.65</v>
+        <v>14083.68</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>745</v>
+        <v>849</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4040.3</v>
+        <v>4564.12</v>
       </c>
       <c r="C7" t="n">
-        <v>4040.3</v>
+        <v>4564.12</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>372</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6377.57</v>
+        <v>7670.79</v>
       </c>
       <c r="C8" t="n">
-        <v>6377.57</v>
+        <v>7670.79</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>391</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69587.93000000001</v>
+        <v>70530.45</v>
       </c>
       <c r="C9" t="n">
-        <v>69587.93000000001</v>
+        <v>70530.45</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-09-28/2025-10-04</t>
+          <t>multi-venue - Sales Summary - 2025-10-05/2025-10-11</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16144.73</v>
+        <v>17802.18</v>
       </c>
       <c r="C3" t="n">
-        <v>16144.73</v>
+        <v>17802.18</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1135</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9341.639999999999</v>
+        <v>11735.93</v>
       </c>
       <c r="C4" t="n">
-        <v>9341.639999999999</v>
+        <v>11735.93</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>588</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18725.49</v>
+        <v>20211.35</v>
       </c>
       <c r="C5" t="n">
-        <v>18725.49</v>
+        <v>20211.35</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1296</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14083.68</v>
+        <v>12708.59</v>
       </c>
       <c r="C6" t="n">
-        <v>14083.68</v>
+        <v>12708.59</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>849</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4564.12</v>
+        <v>6172.34</v>
       </c>
       <c r="C7" t="n">
-        <v>4564.12</v>
+        <v>6172.34</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>404</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7670.79</v>
+        <v>6076.99</v>
       </c>
       <c r="C8" t="n">
-        <v>7670.79</v>
+        <v>6076.99</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>364</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70530.45</v>
+        <v>74707.38</v>
       </c>
       <c r="C9" t="n">
-        <v>70530.45</v>
+        <v>74707.38</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-05/2025-10-11</t>
+          <t>multi-venue - Sales Summary - 2025-10-12/2025-10-18</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17802.18</v>
+        <v>19348.12</v>
       </c>
       <c r="C3" t="n">
-        <v>17802.18</v>
+        <v>19348.12</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1260</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11735.93</v>
+        <v>14158.53</v>
       </c>
       <c r="C4" t="n">
-        <v>11735.93</v>
+        <v>14158.53</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>760</v>
+        <v>903</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20211.35</v>
+        <v>18068.45</v>
       </c>
       <c r="C5" t="n">
-        <v>20211.35</v>
+        <v>18068.45</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1384</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12708.59</v>
+        <v>16241.55</v>
       </c>
       <c r="C6" t="n">
-        <v>12708.59</v>
+        <v>16241.55</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>792</v>
+        <v>932</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6172.34</v>
+        <v>3547.41</v>
       </c>
       <c r="C7" t="n">
-        <v>6172.34</v>
+        <v>3547.41</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>516</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6076.99</v>
+        <v>6649.63</v>
       </c>
       <c r="C8" t="n">
-        <v>6076.99</v>
+        <v>6649.63</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>377</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74707.38</v>
+        <v>78013.69000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>74707.38</v>
+        <v>78013.69000000002</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>

--- a/Acumulado_semanal_ant.xlsx
+++ b/Acumulado_semanal_ant.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>multi-venue - Sales Summary - 2025-10-12/2025-10-18</t>
+          <t>multi-venue - Sales Summary - 2025-10-19/2025-10-25</t>
         </is>
       </c>
     </row>
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19348.12</v>
+        <v>15388.03</v>
       </c>
       <c r="C3" t="n">
-        <v>19348.12</v>
+        <v>15388.03</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -474,7 +474,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1314</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="4">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14158.53</v>
+        <v>9491</v>
       </c>
       <c r="C4" t="n">
-        <v>14158.53</v>
+        <v>9491</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -496,7 +496,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>903</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5">
@@ -506,10 +506,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18068.45</v>
+        <v>16166.77</v>
       </c>
       <c r="C5" t="n">
-        <v>18068.45</v>
+        <v>16166.77</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1246</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6">
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16241.55</v>
+        <v>12980.66</v>
       </c>
       <c r="C6" t="n">
-        <v>16241.55</v>
+        <v>12980.66</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -540,7 +540,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>932</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3547.41</v>
+        <v>5910.44</v>
       </c>
       <c r="C7" t="n">
-        <v>3547.41</v>
+        <v>5910.44</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>310</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6649.63</v>
+        <v>6832.74</v>
       </c>
       <c r="C8" t="n">
-        <v>6649.63</v>
+        <v>6832.74</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -584,7 +584,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>348</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78013.69000000002</v>
+        <v>66769.64000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>78013.69000000002</v>
+        <v>66769.64000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
